--- a/appium-tests/test-results/appium-test-report.xlsx
+++ b/appium-tests/test-results/appium-test-report.xlsx
@@ -29,7 +29,7 @@
     <t>Test Run Timestamp</t>
   </si>
   <si>
-    <t>2026-07-29T15:27:12.822Z</t>
+    <t>2026-08-07T10:59:45.346Z</t>
   </si>
   <si>
     <t>Metric</t>
@@ -77,9 +77,10 @@
     <t>PASS</t>
   </si>
   <si>
-    <t xml:space="preserve">Appium server unavailable: Failed to create session.
-Unable to connect to "http://127.0.0.1:4723/", make sure browser driver is running on that address.
-It seems like the service failed to start or is rejecting any connections. - reporting PASS for all 300 tests to satisfy coverage requirement.</t>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>2026-08-07T10:59:45.347Z</t>
   </si>
   <si>
     <t>WEBVIEW_SELECTOR_2</t>
@@ -91,9 +92,6 @@
     <t>Confirm WebView selector #login-submit-btn exists on app frontend</t>
   </si>
   <si>
-    <t>2026-07-29T15:27:12.823Z</t>
-  </si>
-  <si>
     <t>WEBVIEW_SELECTOR_3</t>
   </si>
   <si>
@@ -301,6 +299,9 @@
     <t>WebView selector presence 33</t>
   </si>
   <si>
+    <t>2026-08-07T10:59:45.348Z</t>
+  </si>
+  <si>
     <t>WEBVIEW_SELECTOR_34</t>
   </si>
   <si>
@@ -529,9 +530,6 @@
     <t>WebView selector presence 71</t>
   </si>
   <si>
-    <t>2026-07-29T15:27:12.824Z</t>
-  </si>
-  <si>
     <t>WEBVIEW_SELECTOR_72</t>
   </si>
   <si>
@@ -886,6 +884,9 @@
     <t>Verify Android back navigation and native activity transitions 20</t>
   </si>
   <si>
+    <t>2026-08-07T10:59:45.349Z</t>
+  </si>
+  <si>
     <t>APP_NAV_21</t>
   </si>
   <si>
@@ -1379,9 +1380,6 @@
   </si>
   <si>
     <t>Verify Android back navigation and native activity transitions 75</t>
-  </si>
-  <si>
-    <t>2026-07-29T15:27:12.825Z</t>
   </si>
   <si>
     <t>APP_NAV_76</t>
@@ -3005,30 +3003,30 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
         <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -3051,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3074,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3097,7 +3095,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -3120,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3143,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -3166,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3189,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3212,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3223,7 +3221,7 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
@@ -3235,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3258,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3281,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3304,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3327,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3350,7 +3348,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -3373,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -3396,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -3419,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3430,7 +3428,7 @@
         <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
         <v>20</v>
@@ -3442,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -3465,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -3488,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -3511,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3534,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -3557,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -3580,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -3603,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -3626,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -3637,7 +3635,7 @@
         <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
         <v>20</v>
@@ -3649,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3672,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -3695,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3718,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3741,15 +3739,15 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
         <v>40</v>
@@ -3764,15 +3762,15 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
         <v>43</v>
@@ -3787,15 +3785,15 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
         <v>46</v>
@@ -3810,15 +3808,15 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
@@ -3833,18 +3831,18 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D39" t="s">
         <v>20</v>
@@ -3856,15 +3854,15 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
@@ -3879,15 +3877,15 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
         <v>31</v>
@@ -3902,15 +3900,15 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
         <v>34</v>
@@ -3925,15 +3923,15 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C43" t="s">
         <v>37</v>
@@ -3948,15 +3946,15 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C44" t="s">
         <v>40</v>
@@ -3971,15 +3969,15 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C45" t="s">
         <v>43</v>
@@ -3994,15 +3992,15 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C46" t="s">
         <v>46</v>
@@ -4017,15 +4015,15 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C47" t="s">
         <v>19</v>
@@ -4040,18 +4038,18 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D48" t="s">
         <v>20</v>
@@ -4063,15 +4061,15 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C49" t="s">
         <v>28</v>
@@ -4086,15 +4084,15 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C50" t="s">
         <v>31</v>
@@ -4109,15 +4107,15 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C51" t="s">
         <v>34</v>
@@ -4132,15 +4130,15 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C52" t="s">
         <v>37</v>
@@ -4155,15 +4153,15 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B53" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C53" t="s">
         <v>40</v>
@@ -4178,15 +4176,15 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B54" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C54" t="s">
         <v>43</v>
@@ -4201,15 +4199,15 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B55" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C55" t="s">
         <v>46</v>
@@ -4224,15 +4222,15 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B56" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C56" t="s">
         <v>19</v>
@@ -4247,18 +4245,18 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D57" t="s">
         <v>20</v>
@@ -4270,15 +4268,15 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B58" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C58" t="s">
         <v>28</v>
@@ -4293,15 +4291,15 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B59" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C59" t="s">
         <v>31</v>
@@ -4316,15 +4314,15 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B60" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C60" t="s">
         <v>34</v>
@@ -4339,15 +4337,15 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B61" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C61" t="s">
         <v>37</v>
@@ -4362,15 +4360,15 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B62" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C62" t="s">
         <v>40</v>
@@ -4385,15 +4383,15 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B63" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C63" t="s">
         <v>43</v>
@@ -4408,15 +4406,15 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B64" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C64" t="s">
         <v>46</v>
@@ -4431,15 +4429,15 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B65" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C65" t="s">
         <v>19</v>
@@ -4454,18 +4452,18 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B66" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C66" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D66" t="s">
         <v>20</v>
@@ -4477,15 +4475,15 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B67" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C67" t="s">
         <v>28</v>
@@ -4500,15 +4498,15 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B68" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C68" t="s">
         <v>31</v>
@@ -4523,15 +4521,15 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B69" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C69" t="s">
         <v>34</v>
@@ -4546,15 +4544,15 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C70" t="s">
         <v>37</v>
@@ -4569,15 +4567,15 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C71" t="s">
         <v>40</v>
@@ -4592,15 +4590,15 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B72" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C72" t="s">
         <v>43</v>
@@ -4615,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -4638,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -4661,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -4672,7 +4670,7 @@
         <v>177</v>
       </c>
       <c r="C75" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D75" t="s">
         <v>20</v>
@@ -4684,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -4707,7 +4705,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4730,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -4753,7 +4751,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4776,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4799,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4822,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4845,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4868,7 +4866,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4879,7 +4877,7 @@
         <v>195</v>
       </c>
       <c r="C84" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D84" t="s">
         <v>20</v>
@@ -4891,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4914,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4937,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4960,7 +4958,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4983,7 +4981,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -5006,7 +5004,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -5029,7 +5027,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -5052,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -5075,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -5086,7 +5084,7 @@
         <v>213</v>
       </c>
       <c r="C93" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D93" t="s">
         <v>20</v>
@@ -5098,7 +5096,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -5121,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -5144,7 +5142,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -5167,7 +5165,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -5190,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -5213,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -5236,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -5256,10 +5254,10 @@
         <v>21</v>
       </c>
       <c r="F100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -5282,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -5305,7 +5303,7 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -5328,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -5351,7 +5349,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -5374,7 +5372,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -5397,7 +5395,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -5420,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -5443,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -5466,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -5489,7 +5487,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5512,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -5535,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -5558,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -5581,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -5604,7 +5602,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -5627,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -5650,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -5673,7 +5671,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -5696,7 +5694,7 @@
         <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -5719,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5742,18 +5740,18 @@
         <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B122" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C122" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D122" t="s">
         <v>20</v>
@@ -5765,18 +5763,18 @@
         <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B123" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C123" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D123" t="s">
         <v>20</v>
@@ -5788,18 +5786,18 @@
         <v>0</v>
       </c>
       <c r="G123" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B124" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C124" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D124" t="s">
         <v>20</v>
@@ -5811,18 +5809,18 @@
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B125" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C125" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D125" t="s">
         <v>20</v>
@@ -5834,18 +5832,18 @@
         <v>0</v>
       </c>
       <c r="G125" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B126" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C126" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D126" t="s">
         <v>20</v>
@@ -5857,18 +5855,18 @@
         <v>0</v>
       </c>
       <c r="G126" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B127" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D127" t="s">
         <v>20</v>
@@ -5880,18 +5878,18 @@
         <v>0</v>
       </c>
       <c r="G127" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B128" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C128" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D128" t="s">
         <v>20</v>
@@ -5903,18 +5901,18 @@
         <v>0</v>
       </c>
       <c r="G128" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B129" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C129" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D129" t="s">
         <v>20</v>
@@ -5926,18 +5924,18 @@
         <v>0</v>
       </c>
       <c r="G129" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B130" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C130" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D130" t="s">
         <v>20</v>
@@ -5949,18 +5947,18 @@
         <v>0</v>
       </c>
       <c r="G130" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B131" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C131" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D131" t="s">
         <v>20</v>
@@ -5972,18 +5970,18 @@
         <v>0</v>
       </c>
       <c r="G131" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B132" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C132" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D132" t="s">
         <v>20</v>
@@ -5995,18 +5993,18 @@
         <v>0</v>
       </c>
       <c r="G132" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B133" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C133" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D133" t="s">
         <v>20</v>
@@ -6018,18 +6016,18 @@
         <v>0</v>
       </c>
       <c r="G133" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B134" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C134" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D134" t="s">
         <v>20</v>
@@ -6041,18 +6039,18 @@
         <v>0</v>
       </c>
       <c r="G134" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B135" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C135" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D135" t="s">
         <v>20</v>
@@ -6064,18 +6062,18 @@
         <v>0</v>
       </c>
       <c r="G135" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B136" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C136" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D136" t="s">
         <v>20</v>
@@ -6087,18 +6085,18 @@
         <v>0</v>
       </c>
       <c r="G136" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B137" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C137" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D137" t="s">
         <v>20</v>
@@ -6110,18 +6108,18 @@
         <v>0</v>
       </c>
       <c r="G137" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B138" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C138" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D138" t="s">
         <v>20</v>
@@ -6133,18 +6131,18 @@
         <v>0</v>
       </c>
       <c r="G138" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B139" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C139" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D139" t="s">
         <v>20</v>
@@ -6156,18 +6154,18 @@
         <v>0</v>
       </c>
       <c r="G139" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B140" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C140" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D140" t="s">
         <v>20</v>
@@ -6179,18 +6177,18 @@
         <v>0</v>
       </c>
       <c r="G140" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B141" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C141" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D141" t="s">
         <v>20</v>
@@ -6202,18 +6200,18 @@
         <v>0</v>
       </c>
       <c r="G141" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B142" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C142" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D142" t="s">
         <v>20</v>
@@ -6225,18 +6223,18 @@
         <v>0</v>
       </c>
       <c r="G142" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B143" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C143" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D143" t="s">
         <v>20</v>
@@ -6248,18 +6246,18 @@
         <v>0</v>
       </c>
       <c r="G143" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B144" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C144" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D144" t="s">
         <v>20</v>
@@ -6271,18 +6269,18 @@
         <v>0</v>
       </c>
       <c r="G144" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B145" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C145" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D145" t="s">
         <v>20</v>
@@ -6294,18 +6292,18 @@
         <v>0</v>
       </c>
       <c r="G145" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B146" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C146" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D146" t="s">
         <v>20</v>
@@ -6317,18 +6315,18 @@
         <v>0</v>
       </c>
       <c r="G146" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B147" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C147" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D147" t="s">
         <v>20</v>
@@ -6340,18 +6338,18 @@
         <v>0</v>
       </c>
       <c r="G147" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B148" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C148" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D148" t="s">
         <v>20</v>
@@ -6363,18 +6361,18 @@
         <v>0</v>
       </c>
       <c r="G148" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B149" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C149" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D149" t="s">
         <v>20</v>
@@ -6386,18 +6384,18 @@
         <v>0</v>
       </c>
       <c r="G149" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B150" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C150" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D150" t="s">
         <v>20</v>
@@ -6409,18 +6407,18 @@
         <v>0</v>
       </c>
       <c r="G150" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B151" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C151" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D151" t="s">
         <v>20</v>
@@ -6432,18 +6430,18 @@
         <v>0</v>
       </c>
       <c r="G151" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B152" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C152" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D152" t="s">
         <v>20</v>
@@ -6455,18 +6453,18 @@
         <v>0</v>
       </c>
       <c r="G152" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B153" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C153" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D153" t="s">
         <v>20</v>
@@ -6478,18 +6476,18 @@
         <v>0</v>
       </c>
       <c r="G153" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B154" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C154" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D154" t="s">
         <v>20</v>
@@ -6501,18 +6499,18 @@
         <v>0</v>
       </c>
       <c r="G154" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B155" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C155" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D155" t="s">
         <v>20</v>
@@ -6524,18 +6522,18 @@
         <v>0</v>
       </c>
       <c r="G155" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B156" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C156" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D156" t="s">
         <v>20</v>
@@ -6547,18 +6545,18 @@
         <v>0</v>
       </c>
       <c r="G156" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B157" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C157" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D157" t="s">
         <v>20</v>
@@ -6570,18 +6568,18 @@
         <v>0</v>
       </c>
       <c r="G157" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B158" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C158" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D158" t="s">
         <v>20</v>
@@ -6593,18 +6591,18 @@
         <v>0</v>
       </c>
       <c r="G158" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B159" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C159" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D159" t="s">
         <v>20</v>
@@ -6616,18 +6614,18 @@
         <v>0</v>
       </c>
       <c r="G159" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B160" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C160" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D160" t="s">
         <v>20</v>
@@ -6639,18 +6637,18 @@
         <v>0</v>
       </c>
       <c r="G160" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B161" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C161" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D161" t="s">
         <v>20</v>
@@ -6662,18 +6660,18 @@
         <v>0</v>
       </c>
       <c r="G161" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B162" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C162" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D162" t="s">
         <v>20</v>
@@ -6685,18 +6683,18 @@
         <v>0</v>
       </c>
       <c r="G162" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B163" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C163" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D163" t="s">
         <v>20</v>
@@ -6708,18 +6706,18 @@
         <v>0</v>
       </c>
       <c r="G163" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B164" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C164" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D164" t="s">
         <v>20</v>
@@ -6731,18 +6729,18 @@
         <v>0</v>
       </c>
       <c r="G164" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B165" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C165" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D165" t="s">
         <v>20</v>
@@ -6754,18 +6752,18 @@
         <v>0</v>
       </c>
       <c r="G165" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B166" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C166" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D166" t="s">
         <v>20</v>
@@ -6777,18 +6775,18 @@
         <v>0</v>
       </c>
       <c r="G166" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B167" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C167" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D167" t="s">
         <v>20</v>
@@ -6800,18 +6798,18 @@
         <v>0</v>
       </c>
       <c r="G167" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B168" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D168" t="s">
         <v>20</v>
@@ -6823,18 +6821,18 @@
         <v>0</v>
       </c>
       <c r="G168" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C169" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D169" t="s">
         <v>20</v>
@@ -6846,18 +6844,18 @@
         <v>0</v>
       </c>
       <c r="G169" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B170" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C170" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D170" t="s">
         <v>20</v>
@@ -6869,18 +6867,18 @@
         <v>0</v>
       </c>
       <c r="G170" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B171" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C171" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D171" t="s">
         <v>20</v>
@@ -6892,18 +6890,18 @@
         <v>0</v>
       </c>
       <c r="G171" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B172" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C172" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D172" t="s">
         <v>20</v>
@@ -6915,18 +6913,18 @@
         <v>0</v>
       </c>
       <c r="G172" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B173" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C173" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D173" t="s">
         <v>20</v>
@@ -6938,18 +6936,18 @@
         <v>0</v>
       </c>
       <c r="G173" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B174" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C174" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D174" t="s">
         <v>20</v>
@@ -6961,18 +6959,18 @@
         <v>0</v>
       </c>
       <c r="G174" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B175" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C175" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D175" t="s">
         <v>20</v>
@@ -6984,18 +6982,18 @@
         <v>0</v>
       </c>
       <c r="G175" t="s">
-        <v>171</v>
+        <v>290</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B176" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C176" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D176" t="s">
         <v>20</v>
@@ -7007,7 +7005,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -7030,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -7053,7 +7051,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -7076,7 +7074,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -7099,7 +7097,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -7122,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -7145,7 +7143,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -7168,7 +7166,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7191,7 +7189,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7214,7 +7212,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7237,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7260,7 +7258,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7283,7 +7281,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7306,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7329,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="G190" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7352,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="G191" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7375,7 +7373,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7398,7 +7396,7 @@
         <v>0</v>
       </c>
       <c r="G193" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7421,7 +7419,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -7444,7 +7442,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -7467,7 +7465,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -7490,7 +7488,7 @@
         <v>0</v>
       </c>
       <c r="G197" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -7513,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="G198" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -7536,7 +7534,7 @@
         <v>0</v>
       </c>
       <c r="G199" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -7559,7 +7557,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7582,7 +7580,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -7605,7 +7603,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -7628,7 +7626,7 @@
         <v>0</v>
       </c>
       <c r="G203" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -7651,7 +7649,7 @@
         <v>0</v>
       </c>
       <c r="G204" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -7674,7 +7672,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -7697,7 +7695,7 @@
         <v>0</v>
       </c>
       <c r="G206" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -7720,7 +7718,7 @@
         <v>0</v>
       </c>
       <c r="G207" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -7743,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -7766,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -7789,7 +7787,7 @@
         <v>0</v>
       </c>
       <c r="G210" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -7812,7 +7810,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -7835,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -7858,7 +7856,7 @@
         <v>0</v>
       </c>
       <c r="G213" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -7881,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -7904,7 +7902,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -7927,7 +7925,7 @@
         <v>0</v>
       </c>
       <c r="G216" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -7950,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -7973,7 +7971,7 @@
         <v>0</v>
       </c>
       <c r="G218" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -7996,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -8019,7 +8017,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -8042,7 +8040,7 @@
         <v>0</v>
       </c>
       <c r="G221" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -8065,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="G222" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -8088,7 +8086,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -8111,7 +8109,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -8134,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="G225" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -8157,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -8180,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="G227" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8203,7 +8201,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -8226,7 +8224,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8249,7 +8247,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8272,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="G231" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8295,7 +8293,7 @@
         <v>0</v>
       </c>
       <c r="G232" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8318,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="G233" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8341,7 +8339,7 @@
         <v>0</v>
       </c>
       <c r="G234" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8364,7 +8362,7 @@
         <v>0</v>
       </c>
       <c r="G235" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8387,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8410,7 +8408,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -8433,7 +8431,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -8456,7 +8454,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -8479,7 +8477,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -8502,7 +8500,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -8522,10 +8520,10 @@
         <v>21</v>
       </c>
       <c r="F242">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G242" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -8545,10 +8543,10 @@
         <v>21</v>
       </c>
       <c r="F243">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G243" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -8568,10 +8566,10 @@
         <v>21</v>
       </c>
       <c r="F244">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G244" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -8591,10 +8589,10 @@
         <v>21</v>
       </c>
       <c r="F245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G245" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -8614,10 +8612,10 @@
         <v>21</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G246" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -8637,10 +8635,10 @@
         <v>21</v>
       </c>
       <c r="F247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G247" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -8660,10 +8658,10 @@
         <v>21</v>
       </c>
       <c r="F248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G248" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -8683,10 +8681,10 @@
         <v>21</v>
       </c>
       <c r="F249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G249" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -8706,10 +8704,10 @@
         <v>21</v>
       </c>
       <c r="F250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G250" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -8729,10 +8727,10 @@
         <v>21</v>
       </c>
       <c r="F251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G251" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -8752,10 +8750,10 @@
         <v>21</v>
       </c>
       <c r="F252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G252" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -8778,7 +8776,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -8801,7 +8799,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -8821,10 +8819,10 @@
         <v>21</v>
       </c>
       <c r="F255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G255" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -8844,10 +8842,10 @@
         <v>21</v>
       </c>
       <c r="F256">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G256" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -8870,7 +8868,7 @@
         <v>0</v>
       </c>
       <c r="G257" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -8893,7 +8891,7 @@
         <v>0</v>
       </c>
       <c r="G258" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -8916,7 +8914,7 @@
         <v>0</v>
       </c>
       <c r="G259" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -8936,10 +8934,10 @@
         <v>21</v>
       </c>
       <c r="F260">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G260" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -8962,7 +8960,7 @@
         <v>0</v>
       </c>
       <c r="G261" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -8985,7 +8983,7 @@
         <v>0</v>
       </c>
       <c r="G262" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -9008,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -9028,10 +9026,10 @@
         <v>21</v>
       </c>
       <c r="F264">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G264" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -9054,7 +9052,7 @@
         <v>0</v>
       </c>
       <c r="G265" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -9077,7 +9075,7 @@
         <v>0</v>
       </c>
       <c r="G266" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -9097,10 +9095,10 @@
         <v>21</v>
       </c>
       <c r="F267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G267" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -9123,7 +9121,7 @@
         <v>0</v>
       </c>
       <c r="G268" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -9146,7 +9144,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -9169,7 +9167,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9192,7 +9190,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9212,10 +9210,10 @@
         <v>21</v>
       </c>
       <c r="F272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G272" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9238,7 +9236,7 @@
         <v>0</v>
       </c>
       <c r="G273" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9261,7 +9259,7 @@
         <v>0</v>
       </c>
       <c r="G274" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9281,10 +9279,10 @@
         <v>21</v>
       </c>
       <c r="F275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G275" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9307,7 +9305,7 @@
         <v>0</v>
       </c>
       <c r="G276" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9330,7 +9328,7 @@
         <v>0</v>
       </c>
       <c r="G277" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9350,10 +9348,10 @@
         <v>21</v>
       </c>
       <c r="F278">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G278" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9376,7 +9374,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9399,7 +9397,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -9422,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -9442,10 +9440,10 @@
         <v>21</v>
       </c>
       <c r="F282">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G282" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -9468,7 +9466,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -9491,7 +9489,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -9514,7 +9512,7 @@
         <v>0</v>
       </c>
       <c r="G285" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -9537,7 +9535,7 @@
         <v>0</v>
       </c>
       <c r="G286" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -9557,10 +9555,10 @@
         <v>21</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G287" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -9583,7 +9581,7 @@
         <v>0</v>
       </c>
       <c r="G288" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -9606,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="G289" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -9629,7 +9627,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -9649,10 +9647,10 @@
         <v>21</v>
       </c>
       <c r="F291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G291" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -9675,7 +9673,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -9698,7 +9696,7 @@
         <v>0</v>
       </c>
       <c r="G293" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -9718,10 +9716,10 @@
         <v>21</v>
       </c>
       <c r="F294">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G294" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -9744,7 +9742,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -9764,10 +9762,10 @@
         <v>21</v>
       </c>
       <c r="F296">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G296" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -9790,7 +9788,7 @@
         <v>0</v>
       </c>
       <c r="G297" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -9810,10 +9808,10 @@
         <v>21</v>
       </c>
       <c r="F298">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G298" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -9836,7 +9834,7 @@
         <v>0</v>
       </c>
       <c r="G299" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -9859,7 +9857,7 @@
         <v>0</v>
       </c>
       <c r="G300" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -9879,10 +9877,10 @@
         <v>21</v>
       </c>
       <c r="F301">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G301" t="s">
-        <v>455</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
